--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136208896</v>
       </c>
       <c r="B37" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>136208803</v>
       </c>
       <c r="B52" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>136209011</v>
       </c>
       <c r="B53" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136208807</v>
       </c>
       <c r="B54" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>136208829</v>
       </c>
       <c r="B55" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136209026</v>
       </c>
       <c r="B56" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
